--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketCalendarInfo001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketCalendarInfo001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19320" windowHeight="5985"/>
@@ -21,7 +21,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>市场日历类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,37 @@
   <si>
     <t>12 伦敦节假日</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13 沪港通交易日历</t>
+  </si>
+  <si>
+    <t>14 深港通交易日历</t>
+  </si>
+  <si>
+    <r>
+      <t>15 沪港通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>深港通交易日历</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -253,7 +284,7 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -262,6 +293,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="Normal_SJNS_SD_TPL_WK_RPT_JP" xfId="7"/>
@@ -301,7 +333,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -343,7 +375,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -378,7 +410,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -587,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.25" style="3" customWidth="1"/>
@@ -665,6 +697,21 @@
     <row r="12" spans="1:9">
       <c r="I12" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="I13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="I14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="I15" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketCalendarInfo001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketCalendarInfo001.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19320" windowHeight="5985"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19320" windowHeight="5988"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>市场日历类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,55 +51,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>01 中国法定节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>02 美国法定节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>03 银行间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04 上交所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>05 深交所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>06 商业银行柜台市场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07 其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>08 香港节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09 澳大利亚节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 欧元区节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11 美元节假日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12 伦敦节假日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -301,7 +253,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -343,7 +295,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -378,7 +330,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -587,20 +539,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.375" customWidth="1"/>
-    <col min="3" max="3" width="18.375" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="8" max="8" width="9.75" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5">
+    <row r="1" spans="1:3" ht="15.6">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -608,73 +559,15 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="I2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="I4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="I6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="I8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="I9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="I11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="I12" t="s">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>$I:$I</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"0 工作日,1 节假日"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"01 中国法定节假日,02 美国法定节假日,03 银行间,04 上交所,05 深交所,06 商业银行柜台市场,07 其他,08 香港节假日,09 澳大利亚节假日,10 欧元区节假日,11 美元节假日,12 伦敦节假日"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -686,7 +579,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -696,7 +589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
